--- a/new test.xlsx
+++ b/new test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vika\Documents\karate\karate_finish\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izrantsevavs\Documents\portfolio\my\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA6301E-8CBD-41BA-8C62-31FDE015D4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F4D8BE-DBF4-46D7-B64B-2C4E9DDA2533}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2014,10 +2014,6 @@
       <c r="N2" s="5">
         <v>3</v>
       </c>
-      <c r="O2" s="5" t="str">
-        <f t="shared" ref="O2:O5" si="0">IF(J2,1, "")</f>
-        <v/>
-      </c>
       <c r="P2" s="5">
         <f>IF(K2="ката",1, "")</f>
         <v>1</v>
@@ -2064,12 +2060,8 @@
       <c r="N3" s="5">
         <v>3</v>
       </c>
-      <c r="O3" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
       <c r="P3" s="5">
-        <f t="shared" ref="P3:P6" si="1">IF(K3="ката",1, "")</f>
+        <f t="shared" ref="P3:P6" si="0">IF(K3="ката",1, "")</f>
         <v>1</v>
       </c>
       <c r="S3" s="12">
@@ -2114,12 +2106,8 @@
       <c r="N4" s="5">
         <v>3</v>
       </c>
-      <c r="O4" s="5" t="str">
+      <c r="P4" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P4" s="5">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S4" s="12">
@@ -2164,12 +2152,8 @@
       <c r="N5" s="5">
         <v>4</v>
       </c>
-      <c r="O5" s="5" t="str">
+      <c r="P5" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P5" s="5">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S5" s="12">
@@ -2214,12 +2198,8 @@
       <c r="N6" s="5">
         <v>4</v>
       </c>
-      <c r="O6" s="5" t="str">
-        <f t="shared" ref="O6:O69" si="2">IF(J6,1, "")</f>
-        <v/>
-      </c>
       <c r="P6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S6" s="12">
@@ -2264,12 +2244,8 @@
       <c r="N7" s="5">
         <v>4</v>
       </c>
-      <c r="O7" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P7" s="5">
-        <f t="shared" ref="P7:P70" si="3">IF(K7="ката",1, "")</f>
+        <f t="shared" ref="P7:P70" si="1">IF(K7="ката",1, "")</f>
         <v>1</v>
       </c>
       <c r="S7" s="12">
@@ -2314,12 +2290,8 @@
       <c r="N8" s="5">
         <v>5</v>
       </c>
-      <c r="O8" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P8" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S8" s="12">
@@ -2364,12 +2336,8 @@
       <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P9" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S9" s="12">
@@ -2411,12 +2379,8 @@
       <c r="N10" s="5">
         <v>5</v>
       </c>
-      <c r="O10" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P10" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S10" s="12">
@@ -2464,12 +2428,8 @@
       <c r="N11" s="5">
         <v>6</v>
       </c>
-      <c r="O11" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P11" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S11" s="12">
@@ -2518,12 +2478,8 @@
       <c r="N12" s="5">
         <v>6</v>
       </c>
-      <c r="O12" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P12" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q12" s="7"/>
@@ -2573,12 +2529,8 @@
       <c r="N13" s="5">
         <v>6</v>
       </c>
-      <c r="O13" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P13" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q13" s="7"/>
@@ -2627,12 +2579,8 @@
       <c r="N14" s="5">
         <v>7</v>
       </c>
-      <c r="O14" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P14" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S14" s="12">
@@ -2680,12 +2628,8 @@
       <c r="N15" s="5">
         <v>7</v>
       </c>
-      <c r="O15" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P15" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S15" s="12">
@@ -2733,12 +2677,8 @@
       <c r="N16" s="5">
         <v>7</v>
       </c>
-      <c r="O16" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P16" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S16" s="12">
@@ -2783,12 +2723,8 @@
       <c r="N17" s="5">
         <v>8</v>
       </c>
-      <c r="O17" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P17" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="S17" s="12">
@@ -2833,12 +2769,8 @@
       <c r="N18" s="5">
         <v>8</v>
       </c>
-      <c r="O18" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P18" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S18" s="12">
@@ -2885,12 +2817,8 @@
       <c r="N19" s="5">
         <v>8</v>
       </c>
-      <c r="O19" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P19" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q19" s="7"/>
@@ -2940,12 +2868,8 @@
       <c r="N20" s="5">
         <v>9</v>
       </c>
-      <c r="O20" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P20" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q20" s="7"/>
@@ -2994,12 +2918,8 @@
       <c r="N21" s="5">
         <v>9</v>
       </c>
-      <c r="O21" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S21" s="12">
@@ -3047,12 +2967,8 @@
       <c r="N22" s="5">
         <v>9</v>
       </c>
-      <c r="O22" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P22" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S22" s="12">
@@ -3100,12 +3016,8 @@
       <c r="N23" s="5">
         <v>10</v>
       </c>
-      <c r="O23" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P23" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S23" s="12">
@@ -3150,12 +3062,8 @@
       <c r="N24" s="5">
         <v>10</v>
       </c>
-      <c r="O24" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P24" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S24" s="12">
@@ -3203,12 +3111,8 @@
       <c r="N25" s="5">
         <v>11</v>
       </c>
-      <c r="O25" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P25" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S25" s="12">
@@ -3256,12 +3160,8 @@
       <c r="N26" s="5">
         <v>11</v>
       </c>
-      <c r="O26" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P26" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S26" s="12">
@@ -3308,12 +3208,8 @@
       <c r="N27" s="5">
         <v>11</v>
       </c>
-      <c r="O27" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P27" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q27" s="7"/>
@@ -3361,12 +3257,8 @@
       <c r="N28" s="5">
         <v>12</v>
       </c>
-      <c r="O28" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P28" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q28" s="7"/>
@@ -3416,12 +3308,8 @@
       <c r="N29" s="5">
         <v>12</v>
       </c>
-      <c r="O29" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P29" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q29" s="7"/>
@@ -3470,12 +3358,8 @@
       <c r="N30" s="5">
         <v>12</v>
       </c>
-      <c r="O30" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P30" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S30" s="12">
@@ -3520,12 +3404,8 @@
       <c r="N31" s="5">
         <v>13</v>
       </c>
-      <c r="O31" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P31" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S31" s="12">
@@ -3573,12 +3453,8 @@
       <c r="N32" s="5">
         <v>13</v>
       </c>
-      <c r="O32" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P32" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S32" s="12">
@@ -3623,12 +3499,8 @@
       <c r="N33" s="5">
         <v>13</v>
       </c>
-      <c r="O33" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P33" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S33" s="12">
@@ -3676,12 +3548,8 @@
       <c r="N34" s="5">
         <v>14</v>
       </c>
-      <c r="O34" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P34" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S34" s="12">
@@ -3729,12 +3597,8 @@
       <c r="N35" s="5">
         <v>14</v>
       </c>
-      <c r="O35" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P35" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S35" s="12">
@@ -3782,12 +3646,8 @@
       <c r="N36" s="5">
         <v>14</v>
       </c>
-      <c r="O36" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P36" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S36" s="12">
@@ -3832,12 +3692,8 @@
       <c r="N37" s="5">
         <v>15</v>
       </c>
-      <c r="O37" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P37" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S37" s="12">
@@ -3882,12 +3738,8 @@
       <c r="N38" s="5">
         <v>15</v>
       </c>
-      <c r="O38" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P38" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S38" s="12">
@@ -3935,12 +3787,8 @@
       <c r="N39" s="5">
         <v>15</v>
       </c>
-      <c r="O39" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P39" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S39" s="12">
@@ -3988,12 +3836,8 @@
       <c r="N40" s="5">
         <v>16</v>
       </c>
-      <c r="O40" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P40" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S40" s="12">
@@ -4041,12 +3885,8 @@
       <c r="N41" s="5">
         <v>16</v>
       </c>
-      <c r="O41" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P41" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S41" s="12">
@@ -4094,12 +3934,8 @@
       <c r="N42" s="5">
         <v>16</v>
       </c>
-      <c r="O42" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P42" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S42" s="12">
@@ -4144,12 +3980,8 @@
       <c r="N43" s="5">
         <v>17</v>
       </c>
-      <c r="O43" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P43" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="S43" s="12">
@@ -4194,12 +4026,8 @@
       <c r="N44" s="5">
         <v>17</v>
       </c>
-      <c r="O44" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P44" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="S44" s="12">
@@ -4244,12 +4072,8 @@
       <c r="N45" s="5">
         <v>17</v>
       </c>
-      <c r="O45" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P45" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S45" s="12">
@@ -4294,12 +4118,8 @@
       <c r="N46" s="5">
         <v>18</v>
       </c>
-      <c r="O46" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P46" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S46" s="12">
@@ -4344,12 +4164,8 @@
       <c r="N47" s="5">
         <v>18</v>
       </c>
-      <c r="O47" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P47" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S47" s="12">
@@ -4394,12 +4210,8 @@
       <c r="N48" s="5">
         <v>18</v>
       </c>
-      <c r="O48" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P48" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S48" s="12">
@@ -4444,12 +4256,8 @@
       <c r="N49" s="5">
         <v>19</v>
       </c>
-      <c r="O49" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P49" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S49" s="12">
@@ -4494,12 +4302,8 @@
       <c r="N50" s="5">
         <v>19</v>
       </c>
-      <c r="O50" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P50" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S50" s="12">
@@ -4544,12 +4348,8 @@
       <c r="N51" s="5">
         <v>19</v>
       </c>
-      <c r="O51" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P51" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S51" s="12">
@@ -4594,12 +4394,8 @@
       <c r="N52" s="5">
         <v>20</v>
       </c>
-      <c r="O52" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P52" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S52" s="12">
@@ -4644,12 +4440,8 @@
       <c r="N53" s="5">
         <v>20</v>
       </c>
-      <c r="O53" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P53" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S53" s="12">
@@ -4694,12 +4486,8 @@
       <c r="N54" s="5">
         <v>20</v>
       </c>
-      <c r="O54" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P54" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S54" s="12">
@@ -4744,12 +4532,8 @@
       <c r="N55" s="5">
         <v>21</v>
       </c>
-      <c r="O55" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P55" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S55" s="12">
@@ -4794,12 +4578,8 @@
       <c r="N56" s="5">
         <v>21</v>
       </c>
-      <c r="O56" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P56" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S56" s="12">
@@ -4844,12 +4624,8 @@
       <c r="N57" s="5">
         <v>21</v>
       </c>
-      <c r="O57" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P57" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S57" s="12">
@@ -4894,12 +4670,8 @@
       <c r="N58" s="5">
         <v>22</v>
       </c>
-      <c r="O58" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P58" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S58" s="12">
@@ -4944,12 +4716,8 @@
       <c r="N59" s="5">
         <v>22</v>
       </c>
-      <c r="O59" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P59" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S59" s="12">
@@ -4994,12 +4762,8 @@
       <c r="N60" s="5">
         <v>22</v>
       </c>
-      <c r="O60" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P60" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S60" s="12">
@@ -5044,12 +4808,8 @@
       <c r="N61" s="5">
         <v>1</v>
       </c>
-      <c r="O61" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P61" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S61" s="12">
@@ -5096,12 +4856,8 @@
       <c r="N62" s="5">
         <v>1</v>
       </c>
-      <c r="O62" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P62" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q62" s="7"/>
@@ -5147,12 +4903,8 @@
       <c r="N63" s="5">
         <v>1</v>
       </c>
-      <c r="O63" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P63" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S63" s="12">
@@ -5197,12 +4949,8 @@
       <c r="N64" s="5">
         <v>2</v>
       </c>
-      <c r="O64" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P64" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S64" s="12">
@@ -5247,12 +4995,8 @@
       <c r="N65" s="5">
         <v>2</v>
       </c>
-      <c r="O65" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P65" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S65" s="12">
@@ -5299,12 +5043,8 @@
       <c r="N66" s="5">
         <v>2</v>
       </c>
-      <c r="O66" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
       <c r="P66" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q66" s="7"/>
@@ -5347,12 +5087,8 @@
       <c r="M67" t="s">
         <v>238</v>
       </c>
-      <c r="O67" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P67" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="S67" s="12">
@@ -5395,12 +5131,8 @@
       <c r="M68" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="O68" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P68" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q68" s="7"/>
@@ -5443,12 +5175,8 @@
       <c r="M69" t="s">
         <v>232</v>
       </c>
-      <c r="O69" s="5">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="P69" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="S69" s="12">
@@ -5490,12 +5218,8 @@
       <c r="M70" t="s">
         <v>266</v>
       </c>
-      <c r="O70" s="5">
-        <f t="shared" ref="O70:O133" si="4">IF(J70,1, "")</f>
-        <v>1</v>
-      </c>
       <c r="P70" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="S70" s="12">
@@ -5537,12 +5261,8 @@
       <c r="M71" t="s">
         <v>229</v>
       </c>
-      <c r="O71" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P71" s="5" t="str">
-        <f t="shared" ref="P71:P134" si="5">IF(K71="ката",1, "")</f>
+        <f t="shared" ref="P71:P134" si="2">IF(K71="ката",1, "")</f>
         <v/>
       </c>
       <c r="S71" s="12">
@@ -5584,12 +5304,8 @@
       <c r="M72" t="s">
         <v>229</v>
       </c>
-      <c r="O72" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P72" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S72" s="12">
@@ -5631,12 +5347,8 @@
       <c r="M73" t="s">
         <v>226</v>
       </c>
-      <c r="O73" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P73" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S73" s="12">
@@ -5678,12 +5390,8 @@
       <c r="M74" t="s">
         <v>226</v>
       </c>
-      <c r="O74" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P74" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S74" s="12">
@@ -5728,12 +5436,8 @@
       <c r="M75" t="s">
         <v>323</v>
       </c>
-      <c r="O75" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P75" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S75" s="12">
@@ -5777,12 +5481,8 @@
       <c r="M76" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="O76" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P76" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q76" s="7"/>
@@ -5825,12 +5525,8 @@
       <c r="M77" t="s">
         <v>257</v>
       </c>
-      <c r="O77" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P77" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S77" s="12">
@@ -5872,12 +5568,8 @@
       <c r="M78" t="s">
         <v>262</v>
       </c>
-      <c r="O78" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P78" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S78" s="12">
@@ -5919,12 +5611,8 @@
       <c r="M79" t="s">
         <v>303</v>
       </c>
-      <c r="O79" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P79" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S79" s="12">
@@ -5966,12 +5654,8 @@
       <c r="M80" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="O80" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P80" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S80" s="12">
@@ -6013,12 +5697,8 @@
       <c r="M81" t="s">
         <v>230</v>
       </c>
-      <c r="O81" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P81" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S81" s="12">
@@ -6062,12 +5742,8 @@
       <c r="M82" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="O82" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P82" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q82" s="7"/>
@@ -6112,12 +5788,8 @@
       <c r="M83" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O83" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P83" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q83" s="7"/>
@@ -6160,12 +5832,8 @@
       <c r="M84" t="s">
         <v>261</v>
       </c>
-      <c r="O84" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P84" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S84" s="12">
@@ -6207,12 +5875,8 @@
       <c r="M85" t="s">
         <v>303</v>
       </c>
-      <c r="O85" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P85" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S85" s="12">
@@ -6254,12 +5918,8 @@
       <c r="M86" t="s">
         <v>258</v>
       </c>
-      <c r="O86" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P86" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S86" s="12">
@@ -6301,12 +5961,8 @@
       <c r="M87" t="s">
         <v>227</v>
       </c>
-      <c r="O87" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P87" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S87" s="12">
@@ -6348,12 +6004,8 @@
       <c r="M88" t="s">
         <v>228</v>
       </c>
-      <c r="O88" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P88" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S88" s="12">
@@ -6395,12 +6047,8 @@
       <c r="M89" t="s">
         <v>276</v>
       </c>
-      <c r="O89" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P89" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S89" s="12">
@@ -6445,12 +6093,8 @@
       <c r="M90" t="s">
         <v>229</v>
       </c>
-      <c r="O90" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P90" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S90" s="12">
@@ -6492,12 +6136,8 @@
       <c r="M91" t="s">
         <v>257</v>
       </c>
-      <c r="O91" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P91" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S91" s="12">
@@ -6539,12 +6179,8 @@
       <c r="M92" t="s">
         <v>330</v>
       </c>
-      <c r="O92" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P92" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S92" s="12">
@@ -6590,12 +6226,8 @@
       <c r="M93" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="O93" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P93" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q93" s="7"/>
@@ -6642,12 +6274,8 @@
       <c r="M94" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="O94" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P94" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Q94" s="7"/>
@@ -6690,12 +6318,8 @@
       <c r="M95" t="s">
         <v>228</v>
       </c>
-      <c r="O95" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P95" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S95" s="12">
@@ -6737,12 +6361,8 @@
       <c r="M96" t="s">
         <v>276</v>
       </c>
-      <c r="O96" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P96" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S96" s="12">
@@ -6784,12 +6404,8 @@
       <c r="M97" t="s">
         <v>276</v>
       </c>
-      <c r="O97" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P97" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S97" s="12">
@@ -6831,12 +6447,8 @@
       <c r="M98" t="s">
         <v>234</v>
       </c>
-      <c r="O98" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P98" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S98" s="12">
@@ -6878,12 +6490,8 @@
       <c r="M99" t="s">
         <v>227</v>
       </c>
-      <c r="O99" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P99" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S99" s="12">
@@ -6925,12 +6533,8 @@
       <c r="M100" t="s">
         <v>314</v>
       </c>
-      <c r="O100" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P100" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S100" s="12">
@@ -6972,12 +6576,8 @@
       <c r="M101" t="s">
         <v>320</v>
       </c>
-      <c r="O101" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P101" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S101" s="12">
@@ -7022,12 +6622,8 @@
       <c r="M102" t="s">
         <v>228</v>
       </c>
-      <c r="O102" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P102" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S102" s="12">
@@ -7069,12 +6665,8 @@
       <c r="M103" t="s">
         <v>228</v>
       </c>
-      <c r="O103" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P103" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S103" s="12">
@@ -7116,12 +6708,8 @@
       <c r="M104" t="s">
         <v>343</v>
       </c>
-      <c r="O104" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P104" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S104" s="12">
@@ -7163,12 +6751,8 @@
       <c r="M105" t="s">
         <v>343</v>
       </c>
-      <c r="O105" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P105" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S105" s="12">
@@ -7210,12 +6794,8 @@
       <c r="M106" t="s">
         <v>257</v>
       </c>
-      <c r="O106" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P106" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S106" s="12">
@@ -7257,12 +6837,8 @@
       <c r="M107" t="s">
         <v>232</v>
       </c>
-      <c r="O107" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P107" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S107" s="12">
@@ -7304,12 +6880,8 @@
       <c r="M108" t="s">
         <v>348</v>
       </c>
-      <c r="O108" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P108" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S108" s="12">
@@ -7351,12 +6923,8 @@
       <c r="M109" t="s">
         <v>232</v>
       </c>
-      <c r="O109" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P109" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S109" s="12">
@@ -7398,12 +6966,8 @@
       <c r="M110" t="s">
         <v>233</v>
       </c>
-      <c r="O110" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P110" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S110" s="12">
@@ -7445,12 +7009,8 @@
       <c r="M111" t="s">
         <v>330</v>
       </c>
-      <c r="O111" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P111" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S111" s="12">
@@ -7492,12 +7052,8 @@
       <c r="M112" t="s">
         <v>257</v>
       </c>
-      <c r="O112" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P112" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S112" s="12">
@@ -7539,12 +7095,8 @@
       <c r="M113" t="s">
         <v>228</v>
       </c>
-      <c r="O113" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P113" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S113" s="12">
@@ -7586,12 +7138,8 @@
       <c r="M114" t="s">
         <v>234</v>
       </c>
-      <c r="O114" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P114" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S114" s="12">
@@ -7633,12 +7181,8 @@
       <c r="M115" t="s">
         <v>352</v>
       </c>
-      <c r="O115" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P115" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S115" s="12">
@@ -7683,12 +7227,8 @@
       <c r="M116" t="s">
         <v>257</v>
       </c>
-      <c r="O116" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P116" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S116" s="12">
@@ -7730,12 +7270,8 @@
       <c r="M117" t="s">
         <v>262</v>
       </c>
-      <c r="O117" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P117" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S117" s="13"/>
@@ -7777,12 +7313,8 @@
       <c r="M118" t="s">
         <v>233</v>
       </c>
-      <c r="O118" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P118" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S118" s="13"/>
@@ -7827,12 +7359,8 @@
       <c r="M119" t="s">
         <v>229</v>
       </c>
-      <c r="O119" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P119" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S119" s="13"/>
@@ -7874,12 +7402,8 @@
       <c r="M120" t="s">
         <v>276</v>
       </c>
-      <c r="O120" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P120" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S120" s="13"/>
@@ -7921,12 +7445,8 @@
       <c r="M121" t="s">
         <v>356</v>
       </c>
-      <c r="O121" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="P121" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S121" s="13"/>
@@ -7968,12 +7488,8 @@
       <c r="M122" t="s">
         <v>231</v>
       </c>
-      <c r="O122" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P122" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S122" s="13"/>
@@ -8015,12 +7531,8 @@
       <c r="M123" t="s">
         <v>361</v>
       </c>
-      <c r="O123" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P123" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S123" s="13"/>
@@ -8062,12 +7574,8 @@
       <c r="M124" t="s">
         <v>343</v>
       </c>
-      <c r="O124" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P124" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S124" s="13"/>
@@ -8109,12 +7617,8 @@
       <c r="M125" t="s">
         <v>314</v>
       </c>
-      <c r="O125" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P125" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S125" s="13"/>
@@ -8156,12 +7660,8 @@
       <c r="M126" t="s">
         <v>231</v>
       </c>
-      <c r="O126" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P126" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S126" s="13"/>
@@ -8203,12 +7703,8 @@
       <c r="M127" t="s">
         <v>320</v>
       </c>
-      <c r="O127" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P127" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S127" s="13"/>
@@ -8250,12 +7746,8 @@
       <c r="M128" t="s">
         <v>307</v>
       </c>
-      <c r="O128" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P128" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S128" s="13"/>
@@ -8297,12 +7789,8 @@
       <c r="M129" t="s">
         <v>262</v>
       </c>
-      <c r="O129" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P129" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S129" s="13"/>
@@ -8344,12 +7832,8 @@
       <c r="M130" t="s">
         <v>230</v>
       </c>
-      <c r="O130" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P130" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S130" s="13"/>
@@ -8391,12 +7875,8 @@
       <c r="M131" t="s">
         <v>307</v>
       </c>
-      <c r="O131" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P131" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S131" s="13"/>
@@ -8438,12 +7918,8 @@
       <c r="M132" t="s">
         <v>224</v>
       </c>
-      <c r="O132" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P132" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S132" s="13"/>
@@ -8485,12 +7961,8 @@
       <c r="M133" t="s">
         <v>343</v>
       </c>
-      <c r="O133" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
       <c r="P133" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S133" s="13"/>
@@ -8532,12 +8004,8 @@
       <c r="M134" t="s">
         <v>343</v>
       </c>
-      <c r="O134" s="5" t="str">
-        <f t="shared" ref="O134:O197" si="6">IF(J134,1, "")</f>
-        <v/>
-      </c>
       <c r="P134" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S134" s="13"/>
@@ -8579,12 +8047,8 @@
       <c r="M135" t="s">
         <v>392</v>
       </c>
-      <c r="O135" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P135" s="5">
-        <f t="shared" ref="P135:P198" si="7">IF(K135="ката",1, "")</f>
+        <f t="shared" ref="P135:P198" si="3">IF(K135="ката",1, "")</f>
         <v>1</v>
       </c>
       <c r="S135" s="13"/>
@@ -8626,12 +8090,8 @@
       <c r="M136" t="s">
         <v>392</v>
       </c>
-      <c r="O136" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P136" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S136" s="13"/>
@@ -8673,12 +8133,8 @@
       <c r="M137" t="s">
         <v>392</v>
       </c>
-      <c r="O137" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P137" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S137" s="13"/>
@@ -8723,12 +8179,8 @@
       <c r="M138" t="s">
         <v>262</v>
       </c>
-      <c r="O138" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P138" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -8766,12 +8218,8 @@
       <c r="M139" t="s">
         <v>226</v>
       </c>
-      <c r="O139" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P139" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -8809,12 +8257,8 @@
       <c r="M140" t="s">
         <v>352</v>
       </c>
-      <c r="O140" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P140" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -8855,12 +8299,8 @@
       <c r="M141" t="s">
         <v>320</v>
       </c>
-      <c r="O141" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P141" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -8898,12 +8338,8 @@
       <c r="M142" t="s">
         <v>266</v>
       </c>
-      <c r="O142" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P142" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -8941,12 +8377,8 @@
       <c r="M143" t="s">
         <v>266</v>
       </c>
-      <c r="O143" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P143" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -8984,12 +8416,8 @@
       <c r="M144" t="s">
         <v>235</v>
       </c>
-      <c r="O144" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P144" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9027,12 +8455,8 @@
       <c r="M145" t="s">
         <v>314</v>
       </c>
-      <c r="O145" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P145" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9070,12 +8494,8 @@
       <c r="M146" t="s">
         <v>314</v>
       </c>
-      <c r="O146" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P146" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9113,12 +8533,8 @@
       <c r="M147" t="s">
         <v>348</v>
       </c>
-      <c r="O147" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P147" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9156,12 +8572,8 @@
       <c r="M148" t="s">
         <v>258</v>
       </c>
-      <c r="O148" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P148" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9199,12 +8611,8 @@
       <c r="M149" t="s">
         <v>257</v>
       </c>
-      <c r="O149" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P149" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9245,12 +8653,8 @@
       <c r="M150" t="s">
         <v>229</v>
       </c>
-      <c r="O150" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P150" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -9291,12 +8695,8 @@
       <c r="M151" t="s">
         <v>348</v>
       </c>
-      <c r="O151" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P151" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -9337,12 +8737,8 @@
       <c r="M152" t="s">
         <v>348</v>
       </c>
-      <c r="O152" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P152" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -9380,12 +8776,8 @@
       <c r="M153" t="s">
         <v>232</v>
       </c>
-      <c r="O153" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P153" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9423,12 +8815,8 @@
       <c r="M154" t="s">
         <v>276</v>
       </c>
-      <c r="O154" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P154" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9466,12 +8854,8 @@
       <c r="M155" t="s">
         <v>235</v>
       </c>
-      <c r="O155" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P155" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9509,12 +8893,8 @@
       <c r="M156" t="s">
         <v>348</v>
       </c>
-      <c r="O156" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P156" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9552,12 +8932,8 @@
       <c r="M157" t="s">
         <v>257</v>
       </c>
-      <c r="O157" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P157" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9598,12 +8974,8 @@
       <c r="M158" t="s">
         <v>307</v>
       </c>
-      <c r="O158" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P158" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -9641,12 +9013,8 @@
       <c r="M159" t="s">
         <v>232</v>
       </c>
-      <c r="O159" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P159" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9684,12 +9052,8 @@
       <c r="M160" t="s">
         <v>232</v>
       </c>
-      <c r="O160" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P160" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9727,12 +9091,8 @@
       <c r="M161" t="s">
         <v>303</v>
       </c>
-      <c r="O161" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P161" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9770,12 +9130,8 @@
       <c r="M162" t="s">
         <v>227</v>
       </c>
-      <c r="O162" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P162" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9813,12 +9169,8 @@
       <c r="M163" t="s">
         <v>348</v>
       </c>
-      <c r="O163" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P163" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9859,12 +9211,8 @@
       <c r="M164" t="s">
         <v>230</v>
       </c>
-      <c r="O164" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P164" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -9902,12 +9250,8 @@
       <c r="M165" t="s">
         <v>234</v>
       </c>
-      <c r="O165" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P165" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9945,12 +9289,8 @@
       <c r="M166" t="s">
         <v>266</v>
       </c>
-      <c r="O166" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P166" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -9988,12 +9328,8 @@
       <c r="M167" t="s">
         <v>229</v>
       </c>
-      <c r="O167" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P167" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10034,12 +9370,8 @@
       <c r="M168" t="s">
         <v>392</v>
       </c>
-      <c r="O168" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P168" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10077,12 +9409,8 @@
       <c r="M169" t="s">
         <v>266</v>
       </c>
-      <c r="O169" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P169" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10120,12 +9448,8 @@
       <c r="M170" t="s">
         <v>276</v>
       </c>
-      <c r="O170" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P170" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10163,12 +9487,8 @@
       <c r="M171" t="s">
         <v>227</v>
       </c>
-      <c r="O171" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P171" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10206,12 +9526,8 @@
       <c r="M172" t="s">
         <v>303</v>
       </c>
-      <c r="O172" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P172" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10249,12 +9565,8 @@
       <c r="M173" t="s">
         <v>266</v>
       </c>
-      <c r="O173" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P173" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10292,12 +9604,8 @@
       <c r="M174" t="s">
         <v>227</v>
       </c>
-      <c r="O174" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P174" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10335,12 +9643,8 @@
       <c r="M175" t="s">
         <v>314</v>
       </c>
-      <c r="O175" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P175" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10378,12 +9682,8 @@
       <c r="M176" t="s">
         <v>231</v>
       </c>
-      <c r="O176" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P176" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10421,12 +9721,8 @@
       <c r="M177" t="s">
         <v>323</v>
       </c>
-      <c r="O177" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P177" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10464,12 +9760,8 @@
       <c r="M178" t="s">
         <v>314</v>
       </c>
-      <c r="O178" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P178" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10507,12 +9799,8 @@
       <c r="M179" t="s">
         <v>228</v>
       </c>
-      <c r="O179" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P179" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10550,12 +9838,8 @@
       <c r="M180" t="s">
         <v>228</v>
       </c>
-      <c r="O180" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
       <c r="P180" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -10593,12 +9877,8 @@
       <c r="M181" t="s">
         <v>323</v>
       </c>
-      <c r="O181" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P181" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10636,12 +9916,8 @@
       <c r="M182" t="s">
         <v>226</v>
       </c>
-      <c r="O182" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P182" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10679,12 +9955,8 @@
       <c r="M183" t="s">
         <v>343</v>
       </c>
-      <c r="O183" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P183" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10722,12 +9994,8 @@
       <c r="M184" t="s">
         <v>261</v>
       </c>
-      <c r="O184" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P184" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10765,12 +10033,8 @@
       <c r="M185" t="s">
         <v>257</v>
       </c>
-      <c r="O185" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P185" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10808,12 +10072,8 @@
       <c r="M186" t="s">
         <v>262</v>
       </c>
-      <c r="O186" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P186" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10851,12 +10111,8 @@
       <c r="M187" t="s">
         <v>261</v>
       </c>
-      <c r="O187" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P187" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10894,12 +10150,8 @@
       <c r="M188" t="s">
         <v>348</v>
       </c>
-      <c r="O188" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P188" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10937,12 +10189,8 @@
       <c r="M189" t="s">
         <v>352</v>
       </c>
-      <c r="O189" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P189" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -10980,12 +10228,8 @@
       <c r="M190" t="s">
         <v>330</v>
       </c>
-      <c r="O190" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P190" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11023,12 +10267,8 @@
       <c r="M191" t="s">
         <v>233</v>
       </c>
-      <c r="O191" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P191" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11069,12 +10309,8 @@
       <c r="M192" t="s">
         <v>320</v>
       </c>
-      <c r="O192" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P192" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -11112,12 +10348,8 @@
       <c r="M193" t="s">
         <v>236</v>
       </c>
-      <c r="O193" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P193" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11155,12 +10387,8 @@
       <c r="M194" t="s">
         <v>314</v>
       </c>
-      <c r="O194" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P194" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11198,12 +10426,8 @@
       <c r="M195" t="s">
         <v>227</v>
       </c>
-      <c r="O195" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P195" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11241,12 +10465,8 @@
       <c r="M196" t="s">
         <v>343</v>
       </c>
-      <c r="O196" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P196" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11284,12 +10504,8 @@
       <c r="M197" t="s">
         <v>348</v>
       </c>
-      <c r="O197" s="5">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="P197" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11327,12 +10543,8 @@
       <c r="M198" t="s">
         <v>348</v>
       </c>
-      <c r="O198" s="5">
-        <f t="shared" ref="O198:O228" si="8">IF(J198,1, "")</f>
-        <v>1</v>
-      </c>
       <c r="P198" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11370,12 +10582,8 @@
       <c r="M199" t="s">
         <v>266</v>
       </c>
-      <c r="O199" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P199" s="5" t="str">
-        <f t="shared" ref="P199:P228" si="9">IF(K199="ката",1, "")</f>
+        <f t="shared" ref="P199:P228" si="4">IF(K199="ката",1, "")</f>
         <v/>
       </c>
     </row>
@@ -11416,12 +10624,8 @@
       <c r="M200" t="s">
         <v>276</v>
       </c>
-      <c r="O200" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P200" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -11459,12 +10663,8 @@
       <c r="M201" t="s">
         <v>261</v>
       </c>
-      <c r="O201" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P201" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11502,12 +10702,8 @@
       <c r="M202" t="s">
         <v>348</v>
       </c>
-      <c r="O202" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P202" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11545,12 +10741,8 @@
       <c r="M203" t="s">
         <v>314</v>
       </c>
-      <c r="O203" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P203" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11588,12 +10780,8 @@
       <c r="M204" t="s">
         <v>348</v>
       </c>
-      <c r="O204" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P204" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11631,12 +10819,8 @@
       <c r="M205" t="s">
         <v>266</v>
       </c>
-      <c r="O205" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P205" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11674,12 +10858,8 @@
       <c r="M206" t="s">
         <v>323</v>
       </c>
-      <c r="O206" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P206" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11717,12 +10897,8 @@
       <c r="M207" t="s">
         <v>262</v>
       </c>
-      <c r="O207" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P207" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11760,12 +10936,8 @@
       <c r="M208" t="s">
         <v>232</v>
       </c>
-      <c r="O208" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P208" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11803,12 +10975,8 @@
       <c r="M209" t="s">
         <v>314</v>
       </c>
-      <c r="O209" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P209" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11846,12 +11014,8 @@
       <c r="M210" t="s">
         <v>348</v>
       </c>
-      <c r="O210" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P210" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11889,12 +11053,8 @@
       <c r="M211" t="s">
         <v>238</v>
       </c>
-      <c r="O211" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P211" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -11935,12 +11095,8 @@
       <c r="M212" t="s">
         <v>225</v>
       </c>
-      <c r="O212" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P212" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -11978,12 +11134,8 @@
       <c r="M213" t="s">
         <v>314</v>
       </c>
-      <c r="O213" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P213" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -12021,12 +11173,8 @@
       <c r="M214" t="s">
         <v>237</v>
       </c>
-      <c r="O214" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P214" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -12064,12 +11212,8 @@
       <c r="M215" t="s">
         <v>237</v>
       </c>
-      <c r="O215" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P215" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -12107,12 +11251,8 @@
       <c r="M216" t="s">
         <v>314</v>
       </c>
-      <c r="O216" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P216" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12150,12 +11290,8 @@
       <c r="M217" t="s">
         <v>307</v>
       </c>
-      <c r="O217" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P217" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12193,12 +11329,8 @@
       <c r="M218" t="s">
         <v>225</v>
       </c>
-      <c r="O218" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P218" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12236,12 +11368,8 @@
       <c r="M219" t="s">
         <v>320</v>
       </c>
-      <c r="O219" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P219" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12279,12 +11407,8 @@
       <c r="M220" t="s">
         <v>307</v>
       </c>
-      <c r="O220" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P220" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12322,12 +11446,8 @@
       <c r="M221" t="s">
         <v>231</v>
       </c>
-      <c r="O221" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P221" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12365,12 +11485,8 @@
       <c r="M222" t="s">
         <v>231</v>
       </c>
-      <c r="O222" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P222" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12408,12 +11524,8 @@
       <c r="M223" t="s">
         <v>478</v>
       </c>
-      <c r="O223" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P223" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12451,12 +11563,8 @@
       <c r="M224" t="s">
         <v>320</v>
       </c>
-      <c r="O224" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
       <c r="P224" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -12494,12 +11602,8 @@
       <c r="M225" t="s">
         <v>483</v>
       </c>
-      <c r="O225" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P225" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -12537,12 +11641,8 @@
       <c r="M226" t="s">
         <v>483</v>
       </c>
-      <c r="O226" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P226" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -12580,12 +11680,8 @@
       <c r="M227" t="s">
         <v>483</v>
       </c>
-      <c r="O227" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P227" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -12623,18 +11719,14 @@
       <c r="M228" t="s">
         <v>483</v>
       </c>
-      <c r="O228" s="5">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
       <c r="P228" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:Q122" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:Q101">
+    <sortState ref="B2:Q101">
       <sortCondition ref="L1"/>
     </sortState>
   </autoFilter>
